--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,1665 @@
           <t>Today</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Send 1st mailer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Send the first mailer as per the calendar sheet to subscribers.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>To maintain a consistent gifting calendar and keep subscribers engaged.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>As per calendar sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fix Product Page Alignment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ensure that the product descriptions are evenly spaced and do not break the alignment on the product page.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A cluttered product page can negatively impact user experience and conversion rates.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correct Grammar in Product Selection</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Review and correct the grammar in the product selection percentage (currently 58%) to ensure accuracy and professionalism.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Grammar errors can undermine the credibility of the brand and negatively impact user trust.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fix Broken CTAs</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Identify and resolve the issue with the CTAs at the bottom of the product page to ensure they are functional and effective.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Broken CTAs can lead to lost sales and revenue opportunities.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finalize Mother's Day Gift Ideas</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Select and finalize gift ideas for Mother's Day, focusing on thoughtful and comforting tea gifts.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>To increase sales and customer satisfaction during the Mother's Day season.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Before Mother's Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Create Email Subject Lines</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Craft email subject lines for Mother's Day promotions, emphasizing comfort, care, and daily joy.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>To grab customers' attention and increase email open rates.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Before sending Mother's Day emails</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finalize Email Campaign for First Flush Tea</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Create and send an email campaign to customers about the First Flush tea, emphasizing its limited availability and freshness.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Increase sales and revenue by promoting a high-demand product.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Go Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Review UK Consumer Emails</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Review all UK consumer emails sent through Klaviyo, including drafts and real ones, up to 180 days, and document them in a single document.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>To understand the current email marketing strategy and identify areas for improvement.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Review Cancellation Flow</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Review the current cancellation flow and identify areas for improvement, including recommended projects and the flow of what happens.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>To ensure a smooth customer experience and minimize cancellations.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Take Screenshots of Campaigns</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Take screenshots of all relevant campaigns related to the cancellation flow and UK consumer emails.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>To document the current state of email marketing campaigns.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Verify Hibiscus Rose Discount Consistency</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Check why Hibiscus Rose is showing 40% off in mailer but 38% off on website globally and ensure consistency across all channels.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Inconsistent discounts can lead to customer confusion and negatively impact sales.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retain Email Flow Documentation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Save the entire document containing all data and flow of emails currently live and running for all email flows.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>To maintain a record of current email flows and data for future reference and improvement.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Integrate chatbot analytics with Vahdam India's existing metrics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Explore the possibility of integrating the chatbot's analytics with Vahdam India's existing metrics to gain a more comprehensive understanding of customer behavior and preferences.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>To better understand customer behavior and preferences, and to make data-driven decisions.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Implement nudges on Vahdam India's PDP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Implement a similar nudge system on Vahdam India's PDP to encourage users to explore more products and increase average order value.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>To increase average order value and encourage users to explore more products.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Develop a recommendation engine for Vahdam India's website</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Develop a recommendation engine that suggests products to users based on their browsing history and preferences.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>To increase sales and improve customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Analyze customer support queries to identify areas for improvement</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Analyze customer support queries to identify areas where Vahdam India can improve its products, services, or customer support.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>To improve customer satisfaction and reduce support queries.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Request for Quote (RFQ)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Send a formal request for quote to the potential agency, outlining Vahdam India's marketing needs and requirements.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>To get a clear understanding of the agency's services and fees.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Discuss View-Only Access with Agency</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Discuss the possibility of granting the agency view-only access to campaigns with the potential agency.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>To ensure seamless collaboration and minimize potential issues.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Prepare Quotation Slab</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Prepare a quotation slab for the agency's fees based on the ad spend bucket (5k-15k dollars).</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>To ensure transparency and clarity in the agency's fees.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Create Production-Ready HTML</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Create production-ready HTML using content shared from Drive by Aman.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>To ensure the content is ready for use in the production environment.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Set 2-hour timer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Set a timer for 2 hours to track the duration of the current conversation.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>To keep track of the conversation duration and ensure the discussion stays focused.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Host Images on Shopify</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Host images on Shopify to improve website performance and reduce loading times.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Better image hosting will improve user experience and potentially increase conversion rates.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Host HTMLs on Shopify</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Host HTMLs on Shopify to ensure consistency and ease of management.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Having HTMLs hosted on Shopify will simplify the process of updating and managing them.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Review UK Landing Pages</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Review the Ashwagandha Coffee Landing Page and the Ashwagandha Coffee Starter Kit page on Vahdam's UK website to ensure they are optimized for conversion.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>To improve conversion rates on the UK website.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Update Canada-Specific Content</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Update the Canada-specific content on Vahdam's website to ensure it is accurate and relevant to the Canadian market.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>To improve the user experience for Canadian customers.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Review Nutrition Support Pages</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Review the Nutrition Support pages on Vahdam's website to ensure they are informative and helpful to customers.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>To improve customer engagement and retention.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Arihant</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Provide UK Data in Specified Format</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Extract and provide UK data from 01-Dec-2025 to 31-Mar-2026 in the specified format.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Anchit needs this data for analysis and decision-making.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>As soon as possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Prepare Price Parity Sheet</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Create a comprehensive price parity sheet comparing Vahdam India's prices across all marketplaces, including Shopify, Amazon US/IN, and other platforms.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>To ensure price parity and maintain a competitive edge across all marketplaces.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Update on Gorilla sheet</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Get an update on the current status of the Gorilla sheet.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Need to understand the current state of the Gorilla sheet to plan further.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Research Amazon Pricing</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Compare Vahdam India's prices with Amazon's prices for similar products to identify any discrepancies.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Understanding price differences can help inform pricing strategies and improve competitiveness.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Complete App Creation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Anshith needs to finish creating his app by the weekend.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>App creation is a priority to move forward with new features and revenue growth.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Anshith</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>by the weekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Review Email List and Body</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Review the email list and body sent by the user and take necessary actions.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Reviewing the email list and body is necessary to understand the context and requirements of the mail.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Follow up on user query</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Respond to the user's query in the DM.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Address the user's concern to provide a good customer experience.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Check Something</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>The recipient needs to check something as requested by Anchit.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Anchit needs this checked to move forward.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Send requested file</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Send the requested file to the user today.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Meet the user's request to send the file today.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Share the item by night</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Share the item with the recipient by the end of the day.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>The recipient is waiting for the item to be shared.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>by night</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Follow up on salary account opening</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Reach out to the bank to inquire about the process and requirements for opening a salary account.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>This will help Subham understand the process and requirements for opening a salary account.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Subham</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Schedule Meeting</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Schedule a meeting with Aman to discuss the same topic.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Need to discuss something with Aman.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>As soon as possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Update on Current Status</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Subham to provide an update on the current status of the topic Anchit inquired about.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Anchit needs to stay informed about the topic.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Subham</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Provide VTAdmin account password</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Share the admin account password (VTAdmin) with Shahzad to help with installing Claude.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Installing Claude requires the admin account password to proceed.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Shahzad</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Provide vtadmin password</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Shehzad needs to share the vtadmin password with Anchit.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Anchit needs access to the vtadmin password for work.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Shehzad</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -653,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -864,6 +2522,1663 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Send 1st mailer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Send the first mailer as per the calendar sheet to subscribers.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>To maintain a consistent gifting calendar and keep subscribers engaged.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>As per calendar sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fix Product Page Alignment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ensure that the product descriptions are evenly spaced and do not break the alignment on the product page.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A cluttered product page can negatively impact user experience and conversion rates.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correct Grammar in Product Selection</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Review and correct the grammar in the product selection percentage (currently 58%) to ensure accuracy and professionalism.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Grammar errors can undermine the credibility of the brand and negatively impact user trust.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fix Broken CTAs</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Identify and resolve the issue with the CTAs at the bottom of the product page to ensure they are functional and effective.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Broken CTAs can lead to lost sales and revenue opportunities.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finalize Mother's Day Gift Ideas</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Select and finalize gift ideas for Mother's Day, focusing on thoughtful and comforting tea gifts.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>To increase sales and customer satisfaction during the Mother's Day season.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Before Mother's Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Create Email Subject Lines</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Craft email subject lines for Mother's Day promotions, emphasizing comfort, care, and daily joy.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>To grab customers' attention and increase email open rates.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Before sending Mother's Day emails</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finalize Email Campaign for First Flush Tea</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Create and send an email campaign to customers about the First Flush tea, emphasizing its limited availability and freshness.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Increase sales and revenue by promoting a high-demand product.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Go Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Review UK Consumer Emails</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Review all UK consumer emails sent through Klaviyo, including drafts and real ones, up to 180 days, and document them in a single document.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>To understand the current email marketing strategy and identify areas for improvement.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Review Cancellation Flow</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Review the current cancellation flow and identify areas for improvement, including recommended projects and the flow of what happens.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>To ensure a smooth customer experience and minimize cancellations.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Take Screenshots of Campaigns</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Take screenshots of all relevant campaigns related to the cancellation flow and UK consumer emails.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>To document the current state of email marketing campaigns.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Verify Hibiscus Rose Discount Consistency</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Check why Hibiscus Rose is showing 40% off in mailer but 38% off on website globally and ensure consistency across all channels.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Inconsistent discounts can lead to customer confusion and negatively impact sales.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retain Email Flow Documentation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Save the entire document containing all data and flow of emails currently live and running for all email flows.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>To maintain a record of current email flows and data for future reference and improvement.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Integrate chatbot analytics with Vahdam India's existing metrics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Explore the possibility of integrating the chatbot's analytics with Vahdam India's existing metrics to gain a more comprehensive understanding of customer behavior and preferences.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>To better understand customer behavior and preferences, and to make data-driven decisions.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Implement nudges on Vahdam India's PDP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Implement a similar nudge system on Vahdam India's PDP to encourage users to explore more products and increase average order value.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>To increase average order value and encourage users to explore more products.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Develop a recommendation engine for Vahdam India's website</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Develop a recommendation engine that suggests products to users based on their browsing history and preferences.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>To increase sales and improve customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Analyze customer support queries to identify areas for improvement</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Analyze customer support queries to identify areas where Vahdam India can improve its products, services, or customer support.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>To improve customer satisfaction and reduce support queries.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>users/110152155675645013355</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Request for Quote (RFQ)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Send a formal request for quote to the potential agency, outlining Vahdam India's marketing needs and requirements.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>To get a clear understanding of the agency's services and fees.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Discuss View-Only Access with Agency</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Discuss the possibility of granting the agency view-only access to campaigns with the potential agency.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>To ensure seamless collaboration and minimize potential issues.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Prepare Quotation Slab</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Prepare a quotation slab for the agency's fees based on the ad spend bucket (5k-15k dollars).</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>To ensure transparency and clarity in the agency's fees.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Create Production-Ready HTML</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Create production-ready HTML using content shared from Drive by Aman.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>To ensure the content is ready for use in the production environment.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Set 2-hour timer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Set a timer for 2 hours to track the duration of the current conversation.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>To keep track of the conversation duration and ensure the discussion stays focused.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Host Images on Shopify</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Host images on Shopify to improve website performance and reduce loading times.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Better image hosting will improve user experience and potentially increase conversion rates.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Host HTMLs on Shopify</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Host HTMLs on Shopify to ensure consistency and ease of management.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Having HTMLs hosted on Shopify will simplify the process of updating and managing them.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Review UK Landing Pages</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Review the Ashwagandha Coffee Landing Page and the Ashwagandha Coffee Starter Kit page on Vahdam's UK website to ensure they are optimized for conversion.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>To improve conversion rates on the UK website.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Update Canada-Specific Content</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Update the Canada-specific content on Vahdam's website to ensure it is accurate and relevant to the Canadian market.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>To improve the user experience for Canadian customers.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Review Nutrition Support Pages</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Review the Nutrition Support pages on Vahdam's website to ensure they are informative and helpful to customers.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>To improve customer engagement and retention.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Arihant</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Provide UK Data in Specified Format</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Extract and provide UK data from 01-Dec-2025 to 31-Mar-2026 in the specified format.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Anchit needs this data for analysis and decision-making.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>As soon as possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Prepare Price Parity Sheet</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Create a comprehensive price parity sheet comparing Vahdam India's prices across all marketplaces, including Shopify, Amazon US/IN, and other platforms.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>To ensure price parity and maintain a competitive edge across all marketplaces.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Update on Gorilla sheet</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Get an update on the current status of the Gorilla sheet.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Need to understand the current state of the Gorilla sheet to plan further.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Research Amazon Pricing</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Compare Vahdam India's prices with Amazon's prices for similar products to identify any discrepancies.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/101892413922856052375</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Understanding price differences can help inform pricing strategies and improve competitiveness.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Complete App Creation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Anshith needs to finish creating his app by the weekend.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>App creation is a priority to move forward with new features and revenue growth.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Anshith</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>by the weekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Review Email List and Body</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Review the email list and body sent by the user and take necessary actions.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Reviewing the email list and body is necessary to understand the context and requirements of the mail.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Follow up on user query</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Respond to the user's query in the DM.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Address the user's concern to provide a good customer experience.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Check Something</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>The recipient needs to check something as requested by Anchit.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Anchit needs this checked to move forward.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Send requested file</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Send the requested file to the user today.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Meet the user's request to send the file today.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Share the item by night</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Share the item with the recipient by the end of the day.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chat | DM with users/112363631041538884730</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>The recipient is waiting for the item to be shared.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>by night</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Follow up on salary account opening</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Reach out to the bank to inquire about the process and requirements for opening a salary account.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>This will help Subham understand the process and requirements for opening a salary account.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Subham</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Schedule Meeting</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Schedule a meeting with Aman to discuss the same topic.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Need to discuss something with Aman.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>As soon as possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Update on Current Status</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Subham to provide an update on the current status of the topic Anchit inquired about.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Anchit needs to stay informed about the topic.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Subham</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Provide VTAdmin account password</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Share the admin account password (VTAdmin) with Shahzad to help with installing Claude.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Installing Claude requires the admin account password to proceed.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Shahzad</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Provide vtadmin password</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Shehzad needs to share the vtadmin password with Anchit.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Anchit needs access to the vtadmin password for work.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Shehzad</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2571,6 +2571,1308 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Follow up with Aman about payment issue</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reach out to Aman to clarify the payment issue and confirm the details of the purchase.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>To resolve the payment issue and ensure customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Configure Growth Pillar</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Configure the growth pillar with the correct name, SPOC, and priority. Ensure it is correctly categorized under Growth, Color, Retention, Acquisition.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>To accurately track and measure growth metrics.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Update the sheet with old content</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Add the old content to the new sheet, and make sure it's not mixed with new content.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>To ensure that the new sheet is accurate and easy to use.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Update status in OOSI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Add a new status to OOSI to track progress and avoid mixing tasks.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>To improve task management and avoid confusion.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Implement WhatsApp APIs</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Explore and implement WhatsApp APIs to integrate with Vahdam India's systems.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>To leverage WhatsApp for customer engagement and communication.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Explore Google Chat API</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Anchit wants to use Google Chat API for automation, as it's free and can be used in place of WhatsApp Business API.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Using Google Chat API can simplify automation and reduce costs.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Create Automated Tracker Project</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Develop an automated tracker project to improve efficiency and accuracy.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>To streamline processes and reduce manual errors.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Create Automated Tracker Project</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Develop an automated tracker project to improve efficiency and accuracy.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>To streamline processes and reduce manual errors.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Verify Landing Page Status</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Check the status of the landing pages, including the final URLs, and ensure they are ready to go live by the 6th of May.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>To ensure timely launch and meet the marketing goals.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Review Dashboard Status</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Verify the production use of the dashboard and ensure it is ready by the 7th of May.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>To ensure timely launch and meet the marketing goals.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Finalize Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Finalize the cadence of creator partnerships and ensure it is completed by the 7th of May.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>To ensure timely launch and meet the marketing goals.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Review Pagedeck Status</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Verify the Pagedeck live on the website and ensure it is ready by the 6th of May.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>To ensure timely launch and meet the marketing goals.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Review Dashboard Progress</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Verify the progress of the production use of the dashboard and ensure it is completed by the specified timeline.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>To ensure timely completion of the dashboard and avoid delays in marketing efforts.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Akhil Arora</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Schedule Landing Page Experts Conversation</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Schedule a final conversation with landing page experts and ensure it is completed by the specified timeline.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>To gather expert insights and drive marketing efforts.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Akhil Arora</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>13th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Review and address feedback from second meeting with Akhil</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Review the feedback from the second meeting with Akhil and address any errors or issues mentioned.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>To ensure that the feedback is addressed and to improve the overall quality of the meeting.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Check lending page buttons</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Verify that the lending page buttons are working properly and troubleshoot any issues. Provide a detailed report to Aman Gupta.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>The lending page buttons not working is a critical issue that needs to be resolved to ensure a smooth user experience.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Review and confirm updated timelines</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Review the updated timelines provided by Aman Gupta and confirm that all tasks are on track to meet the deadlines.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>The updated timelines are crucial to ensure that all tasks are completed on time and that the project stays on track.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Akhil Arora</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Follow up with Aman on lending page issues</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Reach out to Aman Gupta to confirm the status of the lending page buttons and ensure that the issue is resolved.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>To maintain open communication and ensure that the issue is addressed promptly.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Check lending page buttons</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Verify that the lending page buttons are working properly and troubleshoot any issues. Provide a detailed report to Aman Gupta.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>The lending page buttons not working is a critical issue that needs to be resolved to ensure a smooth user experience.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Review and confirm updated timelines</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Review the updated timelines provided by Aman Gupta and confirm that all tasks are on track to meet the deadlines.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>The updated timelines are crucial to ensure that all tasks are completed on time and that the project stays on track.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Akhil Arora</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Follow up with Aman on lending page issues</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Reach out to Aman Gupta to confirm the status of the lending page buttons and ensure that the issue is resolved.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>To maintain open communication and ensure that the issue is addressed promptly.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Check and fix PDP page code</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Aman needs to investigate and resolve the issue with the PDP page not loading, despite HTML working fine. He should check the code and provide a solution to Anchit.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>The PDP page issue is blocking sales and customer experience. Aman needs to resolve this ASAP to prevent further delays.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Troubleshoot PDP issues on Shopify</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Work with Aman to identify and fix the issues with the PDP on Shopify, specifically with HTML, CODI, and Copy.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Fixing the PDP issues will improve the customer experience and potentially increase conversion rates.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Check and fix PDP page code</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Aman needs to investigate and resolve the issue with the PDP page not loading, despite HTML working fine. He should check the code and provide a solution to Anchit.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>The PDP page issue is blocking sales and customer experience. Aman needs to resolve this ASAP to prevent further delays.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Troubleshoot PDP issues on Shopify</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Work with Aman to identify and fix the issues with the PDP on Shopify, specifically with HTML, CODI, and Copy.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fixing the PDP issues will improve the customer experience and potentially increase conversion rates.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Add email data to MOM report</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Include email data, cancellations flows, and winback data in the MOM report as requested by Akhil Arora.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>To provide a comprehensive view of the business performance.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Check lending page buttons</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Verify that the lending page buttons are working properly and fix any issues found.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>To ensure a smooth user experience on the lending page.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Implement Note-Taking and Task-Making System</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Create a system to store notes and tasks from various sources (discussions, meetings, Gmail, WhatsApp) in a centralized location (Google Sheets, Excel, WhatsApp chat) with status update options.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>To improve organization and productivity by having a single source of truth for notes and tasks.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Implement Note-Taking and Task-Making System</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Create a system to store notes and tasks from various sources (discussions, meetings, emails, chats, spaces, groups, WhatsApp chats) in a centralized location (Google Sheets and Excel file) with status update options.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>To improve productivity and organization by having a single source of truth for notes and tasks.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fix HTML coding issue on page deck</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Check and resolve the issue where something doesn't display on the page deck due to HTML coding in the HTML file.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Fixing this issue will improve the user experience and ensure that all content is displayed correctly on the page deck.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2582,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4768,6 +6070,688 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Follow up with Aman about payment issue</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Reach out to Aman to clarify the payment issue and confirm the details of the purchase.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>To resolve the payment issue and ensure customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Configure Growth Pillar</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Configure the growth pillar with the correct name, SPOC, and priority. Ensure it is correctly categorized under Growth, Color, Retention, Acquisition.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>To accurately track and measure growth metrics.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Update the sheet with old content</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Add the old content to the new sheet, and make sure it's not mixed with new content.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>To ensure that the new sheet is accurate and easy to use.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Update status in OOSI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Add a new status to OOSI to track progress and avoid mixing tasks.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>To improve task management and avoid confusion.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Implement WhatsApp APIs</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Explore and implement WhatsApp APIs to integrate with Vahdam India's systems.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>To leverage WhatsApp for customer engagement and communication.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Explore Google Chat API</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Anchit wants to use Google Chat API for automation, as it's free and can be used in place of WhatsApp Business API.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Using Google Chat API can simplify automation and reduce costs.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Create Automated Tracker Project</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Develop an automated tracker project to improve efficiency and accuracy.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>To streamline processes and reduce manual errors.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Create Automated Tracker Project</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Develop an automated tracker project to improve efficiency and accuracy.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>To streamline processes and reduce manual errors.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Review and address feedback from second meeting with Akhil</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Review the feedback from the second meeting with Akhil and address any errors or issues mentioned.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>To ensure that the feedback is addressed and to improve the overall quality of the meeting.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Anchit</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Check and fix PDP page code</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Aman needs to investigate and resolve the issue with the PDP page not loading, despite HTML working fine. He should check the code and provide a solution to Anchit.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>The PDP page issue is blocking sales and customer experience. Aman needs to resolve this ASAP to prevent further delays.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Troubleshoot PDP issues on Shopify</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Work with Aman to identify and fix the issues with the PDP on Shopify, specifically with HTML, CODI, and Copy.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Fixing the PDP issues will improve the customer experience and potentially increase conversion rates.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Check and fix PDP page code</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Aman needs to investigate and resolve the issue with the PDP page not loading, despite HTML working fine. He should check the code and provide a solution to Anchit.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>The PDP page issue is blocking sales and customer experience. Aman needs to resolve this ASAP to prevent further delays.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Troubleshoot PDP issues on Shopify</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Work with Aman to identify and fix the issues with the PDP on Shopify, specifically with HTML, CODI, and Copy.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Fixing the PDP issues will improve the customer experience and potentially increase conversion rates.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Implement Note-Taking and Task-Making System</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Create a system to store notes and tasks from various sources (discussions, meetings, Gmail, WhatsApp) in a centralized location (Google Sheets, Excel, WhatsApp chat) with status update options.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>To improve organization and productivity by having a single source of truth for notes and tasks.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Implement Note-Taking and Task-Making System</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Create a system to store notes and tasks from various sources (discussions, meetings, emails, chats, spaces, groups, WhatsApp chats) in a centralized location (Google Sheets and Excel file) with status update options.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Chat | DM</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>To improve productivity and organization by having a single source of truth for notes and tasks.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Fix HTML coding issue on page deck</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Check and resolve the issue where something doesn't display on the page deck due to HTML coding in the HTML file.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Meeting | voice memo by Anchit (Self)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Fixing this issue will improve the user experience and ensure that all content is displayed correctly on the page deck.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4779,7 +6763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4846,6 +6830,624 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Verify Landing Page Status</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Check the status of the landing pages, including the final URLs, and ensure they are ready to go live by the 6th of May.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>To ensure timely launch and meet the marketing goals.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Review Dashboard Status</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Verify the production use of the dashboard and ensure it is ready by the 7th of May.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>To ensure timely launch and meet the marketing goals.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Finalize Creator Partnerships</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Finalize the cadence of creator partnerships and ensure it is completed by the 7th of May.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>To ensure timely launch and meet the marketing goals.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Review Pagedeck Status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Verify the Pagedeck live on the website and ensure it is ready by the 6th of May.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>To ensure timely launch and meet the marketing goals.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Review Dashboard Progress</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Verify the progress of the production use of the dashboard and ensure it is completed by the specified timeline.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>To ensure timely completion of the dashboard and avoid delays in marketing efforts.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Akhil Arora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Schedule Landing Page Experts Conversation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Schedule a final conversation with landing page experts and ensure it is completed by the specified timeline.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>To gather expert insights and drive marketing efforts.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Akhil Arora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13th May</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Check lending page buttons</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Verify that the lending page buttons are working properly and troubleshoot any issues. Provide a detailed report to Aman Gupta.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>The lending page buttons not working is a critical issue that needs to be resolved to ensure a smooth user experience.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Review and confirm updated timelines</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Review the updated timelines provided by Aman Gupta and confirm that all tasks are on track to meet the deadlines.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The updated timelines are crucial to ensure that all tasks are completed on time and that the project stays on track.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Akhil Arora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Follow up with Aman on lending page issues</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Reach out to Aman Gupta to confirm the status of the lending page buttons and ensure that the issue is resolved.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>To maintain open communication and ensure that the issue is addressed promptly.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Check lending page buttons</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Verify that the lending page buttons are working properly and troubleshoot any issues. Provide a detailed report to Aman Gupta.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The lending page buttons not working is a critical issue that needs to be resolved to ensure a smooth user experience.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Review and confirm updated timelines</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Review the updated timelines provided by Aman Gupta and confirm that all tasks are on track to meet the deadlines.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The updated timelines are crucial to ensure that all tasks are completed on time and that the project stays on track.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Akhil Arora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Follow up with Aman on lending page issues</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Reach out to Aman Gupta to confirm the status of the lending page buttons and ensure that the issue is resolved.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>To maintain open communication and ensure that the issue is addressed promptly.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Anchit Tandon</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Add email data to MOM report</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Include email data, cancellations flows, and winback data in the MOM report as requested by Akhil Arora.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>To provide a comprehensive view of the business performance.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Check lending page buttons</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verify that the lending page buttons are working properly and fix any issues found.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Email | from Akhil Arora</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>To ensure a smooth user experience on the lending page.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Aman Gupta</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -14482,18 +14482,6 @@
   </sheetPr>
   <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -14516,12 +14504,12 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Source Link</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Task Given On</t>
         </is>
@@ -14541,7 +14529,7 @@
           <t>SPOC</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SPOC Contact</t>
         </is>
@@ -14575,18 +14563,6 @@
   </sheetPr>
   <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -14609,12 +14585,12 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Source Link</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Task Given On</t>
         </is>
@@ -14634,7 +14610,7 @@
           <t>SPOC</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SPOC Contact</t>
         </is>
@@ -14670,67 +14646,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task Heading</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Task Description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Source Link</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Task Given On</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Why We're Doing This</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Growth Pillar</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>SPOC</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SPOC Contact</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Task Deadline</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -14749,21 +14725,6 @@
   </sheetPr>
   <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T159"/>
+  <dimension ref="A1:T165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12002,6 +12002,431 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="b">
+        <v>0</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Configure Agent tool for design and HTML mailer creation</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Configure the Agent tool to create design and HTML mailers for our brand.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Streamline our email marketing process and improve design consistency.</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:32.309273+00:00</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="b">
+        <v>0</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Integrate Agent tool for mailer analysis</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Explore the Agent tool for analyzing daily mailers of 200+ DTC brands to understand trends and potential for our brand.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Gain insights from competitors' mailers to inform our own marketing strategies.</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:32.298348+00:00</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="b">
+        <v>0</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Create 5/20 listings for US Detox &amp; Cleanse</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Create product listings for 5/20 products in the US Detox &amp; Cleanse category, focusing on high-conversion and transformation-led products.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>To increase conversion rates and revenue in the US market by offering high-demand products.</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Go Live</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:27.120108+00:00</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="b">
+        <v>0</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Finalize Design Requirements</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ensure the design meets the specified requirements, including a very long vertical layout, rich detailing, and realistic product + ingredient visuals.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>To guarantee the design meets the client's expectations and effectively communicates the brand's message.</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:24.856445+00:00</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="b">
+        <v>0</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Design Email Marketing Campaign</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Create a long-scroll email marketing design for VAHDAM India, incorporating ultra-premium, realistic, and editorial + ecommerce hybrid elements.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>To create a high-end email marketing campaign that showcases VAHDAM India's premium tea brand and drives sales.</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:24.837778+00:00</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="b">
+        <v>0</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Create Project Tracker</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Create a comprehensive project tracker that includes all team members, tasks, statuses, and dependencies.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>To ensure everyone is on the same page and to track progress effectively.</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:22.697869+00:00</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12013,7 +12438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T159"/>
+  <dimension ref="A1:T165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23531,8 +23956,6 @@
           <t>9th May 2026, 3:50 AM</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>open</t>
@@ -23543,7 +23966,6 @@
           <t>Google Chat</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>Google Chat</t>
@@ -23569,7 +23991,6 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>High</t>
@@ -23580,7 +24001,6 @@
           <t>This week</t>
         </is>
       </c>
-      <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
           <t>2026-05-08T22:20:00.852110+00:00</t>
@@ -23589,6 +24009,437 @@
       <c r="T159" t="inlineStr">
         <is>
           <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="b">
+        <v>0</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Configure Agent tool for design and HTML mailer creation</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Configure the Agent tool to create design and HTML mailers for our brand.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Streamline our email marketing process and improve design consistency.</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:32.309273+00:00</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="b">
+        <v>0</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Integrate Agent tool for mailer analysis</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Explore the Agent tool for analyzing daily mailers of 200+ DTC brands to understand trends and potential for our brand.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Gain insights from competitors' mailers to inform our own marketing strategies.</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:32.298348+00:00</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="b">
+        <v>0</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Create 5/20 listings for US Detox &amp; Cleanse</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Create product listings for 5/20 products in the US Detox &amp; Cleanse category, focusing on high-conversion and transformation-led products.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>To increase conversion rates and revenue in the US market by offering high-demand products.</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Go Live</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:27.120108+00:00</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="b">
+        <v>0</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Finalize Design Requirements</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ensure the design meets the specified requirements, including a very long vertical layout, rich detailing, and realistic product + ingredient visuals.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>To guarantee the design meets the client's expectations and effectively communicates the brand's message.</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:24.856445+00:00</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="b">
+        <v>0</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Design Email Marketing Campaign</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Create a long-scroll email marketing design for VAHDAM India, incorporating ultra-premium, realistic, and editorial + ecommerce hybrid elements.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>To create a high-end email marketing campaign that showcases VAHDAM India's premium tea brand and drives sales.</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:24.837778+00:00</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="b">
+        <v>0</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Create Project Tracker</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Create a comprehensive project tracker that includes all team members, tasks, statuses, and dependencies.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>To ensure everyone is on the same page and to track progress effectively.</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:22.697869+00:00</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -23603,7 +24454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T143"/>
+  <dimension ref="A1:T149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -34039,6 +34890,431 @@
       <c r="T143" t="inlineStr">
         <is>
           <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="b">
+        <v>0</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Configure Agent tool for design and HTML mailer creation</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Configure the Agent tool to create design and HTML mailers for our brand.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Streamline our email marketing process and improve design consistency.</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:32.309273+00:00</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="b">
+        <v>0</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Integrate Agent tool for mailer analysis</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Explore the Agent tool for analyzing daily mailers of 200+ DTC brands to understand trends and potential for our brand.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Gain insights from competitors' mailers to inform our own marketing strategies.</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:32.298348+00:00</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="b">
+        <v>0</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Create 5/20 listings for US Detox &amp; Cleanse</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Create product listings for 5/20 products in the US Detox &amp; Cleanse category, focusing on high-conversion and transformation-led products.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>To increase conversion rates and revenue in the US market by offering high-demand products.</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Go Live</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:27.120108+00:00</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="b">
+        <v>0</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Finalize Design Requirements</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ensure the design meets the specified requirements, including a very long vertical layout, rich detailing, and realistic product + ingredient visuals.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>To guarantee the design meets the client's expectations and effectively communicates the brand's message.</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:24.856445+00:00</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="b">
+        <v>0</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Design Email Marketing Campaign</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Create a long-scroll email marketing design for VAHDAM India, incorporating ultra-premium, realistic, and editorial + ecommerce hybrid elements.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>To create a high-end email marketing campaign that showcases VAHDAM India's premium tea brand and drives sales.</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:24.837778+00:00</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="b">
+        <v>0</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Create Project Tracker</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Create a comprehensive project tracker that includes all team members, tasks, statuses, and dependencies.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>9th May 2026, 3:49 AM</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Google Chat</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>To ensure everyone is on the same page and to track progress effectively.</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Team &amp; Process</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>2026-05-08T22:19:22.697869+00:00</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
